--- a/test_codes/table_alignment_results.xlsx
+++ b/test_codes/table_alignment_results.xlsx
@@ -1,18 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表格_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表格_2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表格_3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表格_4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表格_5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="汇总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P158_表格_1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="P158_表格_2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -503,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>其他应付款</t>
+          <t>各支行存款情况</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,20 +508,26 @@
           <t>是</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>0.9875</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -533,7 +536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>租赁负债</t>
+          <t>与最大十户集团信贷客户的交易情况</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -541,110 +544,30 @@
           <t>是</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2023年12月31日</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9958333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>172</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>预计负债</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>应付债券</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>递延所得税负债</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>22</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -675,226 +598,187 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>机构名称</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>2023年12月31日</t>
+          <t>存款总额</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>2023年12月31日</t>
+          <t>占总存款比例</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 打包股股利</t>
+          <t>新塍支行</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>711,912.19</t>
+          <t>124,023.59</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>711,912.19</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 待解报单暂收</t>
+          <t>建设支行</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>610,087.17</t>
+          <t>141,419.63</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>588,837.90</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 中间业务暂收款</t>
+          <t>新塍支行</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>407,117.37</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr"/>
+          <t>128,107.42</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 待处理出纳长款</t>
+          <t>经开支行</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
+          <t>285,785.10</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>3.83%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 应付市场平盘款项</t>
+          <t>开发区支行</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>13,021,939.60</t>
+          <t>226,150.37</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>23,575,690.00</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 待清算银行卡跨行资金</t>
+          <t>桃园支行</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>752,375.10</t>
+          <t>105,288.98</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>752,356.66</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 久悬未取款</t>
+          <t>高新支行</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>16,099,894.14</t>
+          <t>95,309.92</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>15,889,757.38</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 股金业务暂挂</t>
+          <t>嘉北支行</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2,770,389.46</t>
+          <t>67,606.09</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>4,739,084.04</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 财务暂收</t>
+          <t>塘汇支行</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>9,487,268.79</t>
+          <t>81,754.36</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>14,645,395.73</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 电子商城待结算款项</t>
+          <t>汇总</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>12,584.05</t>
+          <t>7,470,186.64</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>575.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 红包待结算款项</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 其他应付款</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>l4,752,319.65</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>10,092,327.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 合计</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>58,625,888.52</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>70,995,939.95</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -909,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -926,423 +810,652 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>2023年12月31日</t>
+          <t>户名</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>2023年12月31日</t>
+          <t>贷款</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>承兑汇票</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>贴现</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>占资本净额比例</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>贷款担保方式</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>五级分类</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>存款</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>其中：保证金</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 &gt; 租赁付款额</t>
+          <t>1
+2
+3
+4</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>48,619,699.57</t>
+          <t>五芳斋集团股份有限公司</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>57,594,267.68</t>
-        </is>
-      </c>
+          <t>30,000.00</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>30,000.00</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>信用2000、
+抵押28000</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 未确认融资费用</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>-4,249,497.49</t>
+          <t>五芳斋集团股份有限公司 &gt; 小计</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>~5,494,688.18</t>
-        </is>
-      </c>
+          <t>30,000.00</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>30,000.00</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 合计</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>44,370,202.08</t>
+          <t>浙江优百特电器有限公司</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>52,099,579.50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>2023年12月31日</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>2023年12月31日</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 银行承兑汇票计提损失准备</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>4,532,427.83</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2,829,422.16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 开出国内远期信用证计提损失准备</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>1,282,254.04</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>7,713,194.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 开出非融资保函款项计提损失准备</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>160,270.68</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>94,203.02</t>
-        </is>
-      </c>
+          <t>9,500.00</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1,061.29</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>10,561.29</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 合计</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>5,974,952.55</t>
+          <t>嘉兴苏古德塑业股份有限公司</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>10,636,819.28</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>2023年12月31日</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>2023年12月31日</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 次级债券</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>899,881,732.45</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>899,568,246.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 同业存单</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>447,639,485.66</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>1,120,245,252.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 加：应计利息</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>18,693,989.05</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>18,745,205.49</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 合计</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>1,366,215,207.16</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2,038,558,704.90</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>2023年12月31日 &gt; 应纳税暂时性差异</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>2023年12月31日 &gt; 递延所得税负债</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>2022年12月31日 &gt; 应纳税暂时性差异</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>2022年12月31日 &gt; 递延所得税负债</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 贷款应计收利息</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>67,410,979.47</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>l6,852,744.87</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>65,868,062.29</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>16,467,015.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 500.00万元以下固定资产折旧</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>21,509,333.70</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>5,377,333.43</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>29,227,923.11</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>7,306,980.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>项目 &gt; 交易性金融资产公允价值变动</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>381,665,712.37</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>95,416,428.09</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>265,047,631.19</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>66,261,907.80</t>
-        </is>
-      </c>
+          <t>1,000.00</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>1,000.00</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>浙江手拉手电器科技有限公司</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>7,900.00</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>7,900.00</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>手拉手纳米科技（嘉兴）有限公司</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>7,000.00</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>7,000.00</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>浙江优杰特商贸股份有限公司</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>手拉手（浙江）智能家居有限公司</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>4,500.00</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>4,500.00</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>五芳斋集团股份有限公司 &gt; 小计</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>30,500.00</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1,061.29</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>31,561.29</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>3.83%</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>嘉兴特钢新城开发有限公司</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>9,990.00</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>9,990.00</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>保证</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>嘉兴市嘉凤生态农业开发有限公司</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>1,495.00</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>1,495.00</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>保证</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>嘉兴市嘉南投资发展有限公司</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>10,000.00</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>10,000.00</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>保证</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>嘉兴创意投资开发有限公司</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>19,990.00</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>19,990.00</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>2.43%</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>保证</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>嘉兴创意投资开发有限公司</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>14,900.00</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>14,900.00</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>保证</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>五芳斋集团股份有限公司 &gt; 小计</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>56,375.00</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>56,375.00</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>6.84%</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>浙江江德不锈钢管业股份有限公司</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>13,850.00</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>13,850.00</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>信用6000
+抵押7850</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
